--- a/data/trans_orig/P41D_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P41D_2023-Clase-trans_orig.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si con respecto a la última vez que lo intentaron se quedó embarazada en 2023</t>
+          <t>Población según si con respecto a la última vez que lo intentaron se quedó embarazada en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,03%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>592</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1221,62 +1221,62 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
           <t>3810</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>63,75%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>3810</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>2429</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3810</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2473</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2473</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1529,97 +1529,97 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
           <t>4345</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>4345</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1872</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>4345</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>78,88%</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2435,107 +2435,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>831</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6065</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4154</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9230</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,3%</t>
         </is>
       </c>
     </row>
@@ -2548,107 +2548,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11233</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7236</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9252</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17162</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12086</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20126</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -2661,462 +2661,119 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11233</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11233</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11233</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10083</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10083</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10083</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21316</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21316</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21316</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>1307</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5776</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>11,64%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>51,42%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>2847</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>855</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>6551</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>28,23%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>8,48%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>64,97%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>4154</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>1167</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>9247</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>19,49%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>43,38%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>9926</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>5462</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>11233</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>88,36%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>48,62%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>7236</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>9228</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>71,77%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>35,03%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>91,52%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>17162</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>12069</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>20149</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>80,51%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>56,62%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>94,52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>11233</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>11233</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>11233</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>10083</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>10083</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>10083</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>21316</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>21316</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>21316</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -3126,7 +2783,6 @@
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_orig/P41D_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P41D_2023-Clase-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,84%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>663</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>617</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>771</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1834,12 +1834,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>83,16%</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2296</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1877,12 +1877,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1937,27 +1937,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>964</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>5727</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>5727</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>5727</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>5727</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6044</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>811</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>6073</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9230</t>
+          <t>9511</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,76%</t>
         </is>
       </c>
     </row>
@@ -2553,27 +2553,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>10633</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11233</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7236</t>
+          <t>7506</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>9539</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>17162</t>
+          <t>18138</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12086</t>
+          <t>12733</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20126</t>
+          <t>21141</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11233</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11233</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11233</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10083</t>
+          <t>10350</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10083</t>
+          <t>10350</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10083</t>
+          <t>10350</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>21316</t>
+          <t>22244</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21316</t>
+          <t>22244</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21316</t>
+          <t>22244</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
